--- a/artfynd/A 29332-2023 artfynd.xlsx
+++ b/artfynd/A 29332-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 29332-2023 artfynd.xlsx
+++ b/artfynd/A 29332-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY21"/>
+  <dimension ref="A1:AY20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2919,122 +2919,6 @@
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>110400096</v>
-      </c>
-      <c r="B21" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E21" t="n">
-        <v>6458</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Lunglav</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>Lobaria pulmonaria</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t>Östboda, Jmt</t>
-        </is>
-      </c>
-      <c r="Q21" t="n">
-        <v>510249.6328330836</v>
-      </c>
-      <c r="R21" t="n">
-        <v>6952834.65716501</v>
-      </c>
-      <c r="S21" t="n">
-        <v>10</v>
-      </c>
-      <c r="T21" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U21" t="inlineStr">
-        <is>
-          <t>Bräcke</t>
-        </is>
-      </c>
-      <c r="V21" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W21" t="inlineStr">
-        <is>
-          <t>Bodsjö</t>
-        </is>
-      </c>
-      <c r="Y21" t="inlineStr">
-        <is>
-          <t>2023-06-26</t>
-        </is>
-      </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA21" t="inlineStr">
-        <is>
-          <t>2023-06-26</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD21" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE21" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF21" t="inlineStr"/>
-      <c r="AG21" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT21" t="inlineStr"/>
-      <c r="AW21" t="inlineStr">
-        <is>
-          <t>Erik Söderhjelm</t>
-        </is>
-      </c>
-      <c r="AX21" t="inlineStr">
-        <is>
-          <t>Erik Söderhjelm</t>
-        </is>
-      </c>
-      <c r="AY21" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
